--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.95605622296915</v>
+        <v>6.005359136232488</v>
       </c>
       <c r="D2" t="n">
-        <v>37.76774974909928</v>
+        <v>6.137259334228633</v>
       </c>
       <c r="E2" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F2" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.39404157385322</v>
+        <v>7.376531755751149</v>
       </c>
       <c r="D3" t="n">
-        <v>46.40530392873155</v>
+        <v>7.540861888418877</v>
       </c>
       <c r="E3" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F3" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.85887336542169</v>
+        <v>8.264566921881025</v>
       </c>
       <c r="D4" t="n">
-        <v>52.19967272612161</v>
+        <v>8.482446817994763</v>
       </c>
       <c r="E4" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F4" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.10286049297462</v>
+        <v>3.266714830108377</v>
       </c>
       <c r="D5" t="n">
-        <v>25.57577663150209</v>
+        <v>4.15606370261909</v>
       </c>
       <c r="E5" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F5" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.25313179261851</v>
+        <v>4.266133916300509</v>
       </c>
       <c r="D6" t="n">
-        <v>39.56858905222282</v>
+        <v>6.429895720986209</v>
       </c>
       <c r="E6" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F6" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>44.58575548586964</v>
+        <v>7.245185266453817</v>
       </c>
       <c r="D7" t="n">
-        <v>44.16378482836895</v>
+        <v>7.176615034609954</v>
       </c>
       <c r="E7" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F7" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>42.33033852156478</v>
+        <v>6.878680009754277</v>
       </c>
       <c r="D8" t="n">
-        <v>42.0924519375144</v>
+        <v>6.84002343984609</v>
       </c>
       <c r="E8" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F8" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>48.77548319494394</v>
+        <v>7.92601601917839</v>
       </c>
       <c r="D9" t="n">
-        <v>48.79575457840838</v>
+        <v>7.929310118991362</v>
       </c>
       <c r="E9" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F9" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>14.25677097150488</v>
+        <v>2.316725282869544</v>
       </c>
       <c r="D10" t="n">
-        <v>14.09524049494513</v>
+        <v>2.290476580428584</v>
       </c>
       <c r="E10" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F10" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>8.89519417868447</v>
+        <v>1.445469054036226</v>
       </c>
       <c r="D11" t="n">
-        <v>8.243736665789127</v>
+        <v>1.339607208190733</v>
       </c>
       <c r="E11" t="n">
-        <v>14.47580485356524</v>
+        <v>2.352318288704352</v>
       </c>
       <c r="F11" t="n">
-        <v>14.18742416638505</v>
+        <v>2.305456427037571</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
